--- a/output/graficos_regionales/plot_regional_serie_i_ingr_mean_m_2018_metropolitana.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_mean_m_2018_metropolitana.xlsx
@@ -288,7 +288,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:47</t>
+    <t xml:space="preserve">2026-10-05 02:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -704,7 +704,7 @@
         <v>373870.88</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>307926.12</v>
+        <v>307926.13</v>
       </c>
     </row>
     <row r="3">
@@ -789,7 +789,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>406856.12</v>
+        <v>406856.13</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>330408.25</v>
@@ -847,7 +847,7 @@
         <v>396250.22</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>324105.12</v>
+        <v>324105.13</v>
       </c>
     </row>
     <row r="16">
@@ -913,7 +913,7 @@
         <v>405324.94</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>329863.62</v>
+        <v>329863.63</v>
       </c>
     </row>
     <row r="22">
@@ -921,7 +921,7 @@
         <v>23</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>422978.62</v>
+        <v>422978.63</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>345530</v>
@@ -987,7 +987,7 @@
         <v>29</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>408421.12</v>
+        <v>408421.13</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>338426.22</v>
@@ -998,7 +998,7 @@
         <v>30</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>385663.62</v>
+        <v>385663.63</v>
       </c>
       <c r="C29" s="2" t="n">
         <v>318143.44</v>
@@ -1287,7 +1287,7 @@
         <v>471245.38</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>391178.62</v>
+        <v>391178.63</v>
       </c>
     </row>
     <row r="56">
@@ -1529,7 +1529,7 @@
         <v>532360.25</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>440497.12</v>
+        <v>440497.13</v>
       </c>
     </row>
     <row r="78">
@@ -1595,7 +1595,7 @@
         <v>544533</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>451935.62</v>
+        <v>451935.63</v>
       </c>
     </row>
     <row r="84">
